--- a/MattsRpath/RPath_parameterdraftlist.xlsx
+++ b/MattsRpath/RPath_parameterdraftlist.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cawater-my.sharepoint.com/personal/rosemary_hartman_water_ca_gov/Documents/food webs/FoodwebModel/MattsRpath/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="502" documentId="8_{6BDD44C6-9D4B-4160-A4C5-B8CC2CF85AEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF1B18A8-A493-4930-A18D-5A2C4CE8DC1B}"/>
+  <xr:revisionPtr revIDLastSave="556" documentId="8_{6BDD44C6-9D4B-4160-A4C5-B8CC2CF85AEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6490C885-7DB3-4181-AF35-6514DD7C1C59}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00E913D7-4E82-4E87-9828-59006E2DA130}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00E913D7-4E82-4E87-9828-59006E2DA130}"/>
   </bookViews>
   <sheets>
     <sheet name="Matt's origional" sheetId="1" r:id="rId1"/>
-    <sheet name="testparams" sheetId="5" r:id="rId2"/>
-    <sheet name="dietmatrix" sheetId="6" r:id="rId3"/>
-    <sheet name="New params" sheetId="2" r:id="rId4"/>
-    <sheet name="StableIsotopDiets" sheetId="3" r:id="rId5"/>
-    <sheet name="Schroeteretal2015" sheetId="4" r:id="rId6"/>
+    <sheet name="biomassPerHabitat" sheetId="7" r:id="rId2"/>
+    <sheet name="testparams" sheetId="5" r:id="rId3"/>
+    <sheet name="dietmatrix" sheetId="6" r:id="rId4"/>
+    <sheet name="New params" sheetId="2" r:id="rId5"/>
+    <sheet name="StableIsotopDiets" sheetId="3" r:id="rId6"/>
+    <sheet name="Schroeteretal2015" sheetId="4" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -314,7 +315,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="178">
   <si>
     <t>Site</t>
   </si>
@@ -812,6 +813,42 @@
   </si>
   <si>
     <t>Import</t>
+  </si>
+  <si>
+    <t>PredatoryCopepods</t>
+  </si>
+  <si>
+    <t>OtherCopepods</t>
+  </si>
+  <si>
+    <t>Limnoithona</t>
+  </si>
+  <si>
+    <t>Emergent</t>
+  </si>
+  <si>
+    <t>FAV</t>
+  </si>
+  <si>
+    <t>Water</t>
+  </si>
+  <si>
+    <t>Soil/mudflat</t>
+  </si>
+  <si>
+    <t>Confluence</t>
+  </si>
+  <si>
+    <t>Grizzly</t>
+  </si>
+  <si>
+    <t>Decker</t>
+  </si>
+  <si>
+    <t>Webb</t>
+  </si>
+  <si>
+    <t>x</t>
   </si>
 </sst>
 </file>
@@ -3675,8 +3712,470 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8675226-D191-481E-B450-083710A2914C}">
+  <dimension ref="A1:G46"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="23.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>113</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>173</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>173</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>173</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>173</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>173</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>173</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>173</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>173</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>173</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>174</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>174</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>174</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>174</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>174</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>174</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>174</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>174</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>174</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>175</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>175</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>175</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>175</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>175</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>175</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>175</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>175</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>175</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>176</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>176</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>176</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>176</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>176</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>176</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>176</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>176</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>176</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D90776B-D387-4A99-8EF1-CBCC147CD9BF}">
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.26953125" bestFit="1" customWidth="1"/>
@@ -3748,7 +4247,7 @@
         <v>10</v>
       </c>
       <c r="G2" s="3">
-        <f t="shared" ref="G2:G11" si="0">E2/F2</f>
+        <f t="shared" ref="G2:G10" si="0">E2/F2</f>
         <v>0.12</v>
       </c>
       <c r="H2">
@@ -3772,321 +4271,201 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B3" s="3">
-        <v>0</v>
-      </c>
-      <c r="C3" s="3">
-        <v>2.8140000000000001</v>
-      </c>
-      <c r="D3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3">
+        <v>5878.5240000000003</v>
+      </c>
+      <c r="D7" t="s">
         <v>156</v>
       </c>
-      <c r="E3" s="5">
-        <v>2</v>
-      </c>
-      <c r="F3" s="3">
-        <v>10</v>
-      </c>
-      <c r="G3" s="3">
-        <f t="shared" si="0"/>
-        <v>0.2</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0.2</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3" s="3">
-        <v>0</v>
-      </c>
-      <c r="M3" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="B4" s="10">
-        <v>0</v>
-      </c>
-      <c r="C4" s="3">
-        <v>5878.5240000000003</v>
-      </c>
-      <c r="D4" t="s">
-        <v>156</v>
-      </c>
-      <c r="E4" s="5">
+      <c r="E7" s="5">
         <v>3</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F7" s="3">
         <v>5</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G7" s="3">
         <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
         <v>0.2</v>
       </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
         <v>1</v>
       </c>
-      <c r="L4" s="3">
-        <v>0</v>
-      </c>
-      <c r="M4" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
+      <c r="L7" s="3">
+        <v>0</v>
+      </c>
+      <c r="M7" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="3">
-        <v>0</v>
-      </c>
-      <c r="C5" s="3">
+      <c r="B8" s="3">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3">
         <v>11.471</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D8" t="s">
         <v>156</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E8" s="5">
         <v>3</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F8" s="3">
         <v>5</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G8" s="3">
         <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
         <v>0.2</v>
       </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
         <v>1</v>
       </c>
-      <c r="L5" s="3">
-        <v>0</v>
-      </c>
-      <c r="M5" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A6" s="10" t="s">
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="10">
-        <v>0</v>
-      </c>
-      <c r="C6" s="3">
+      <c r="B9" s="3">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3">
         <v>2934.8919999999998</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D9" t="s">
         <v>156</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E9" s="5">
         <v>3</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F9" s="3">
         <v>5</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G9" s="3">
         <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
         <v>0.2</v>
       </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
         <v>1</v>
       </c>
-      <c r="L6" s="3">
-        <v>0</v>
-      </c>
-      <c r="M6" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B7" s="3">
-        <v>0</v>
-      </c>
-      <c r="C7" s="3">
-        <v>0.38600000000000001</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="L9" s="3">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" s="3">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0.218</v>
+      </c>
+      <c r="D10" t="s">
         <v>156</v>
       </c>
-      <c r="E7" s="5">
-        <v>2</v>
-      </c>
-      <c r="F7" s="3">
-        <v>12</v>
-      </c>
-      <c r="G7" s="3">
-        <f t="shared" si="0"/>
-        <v>0.16666666666666666</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0.2</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7" s="3">
-        <v>0</v>
-      </c>
-      <c r="M7" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B8" s="3">
-        <v>0</v>
-      </c>
-      <c r="C8" s="3">
-        <v>0.218</v>
-      </c>
-      <c r="D8" t="s">
-        <v>156</v>
-      </c>
-      <c r="E8" s="5">
+      <c r="E10" s="5">
         <v>57.3</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F10" s="3">
         <v>100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G10" s="3">
         <f t="shared" si="0"/>
         <v>0.57299999999999995</v>
       </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0.2</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>1</v>
-      </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B9" s="3">
-        <v>0</v>
-      </c>
-      <c r="C9" s="3">
-        <v>30.882999999999999</v>
-      </c>
-      <c r="D9" t="s">
-        <v>156</v>
-      </c>
-      <c r="E9" s="5">
-        <v>52.02</v>
-      </c>
-      <c r="F9" s="3">
-        <v>100</v>
-      </c>
-      <c r="G9" s="3">
-        <f t="shared" si="0"/>
-        <v>0.5202</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0.2</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>1</v>
-      </c>
-      <c r="L9" s="3">
-        <v>0</v>
-      </c>
-      <c r="M9" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B10" s="3">
-        <v>0</v>
-      </c>
-      <c r="C10" s="3">
-        <v>0.63600000000000001</v>
-      </c>
-      <c r="D10" t="s">
-        <v>156</v>
-      </c>
-      <c r="E10" s="5">
-        <v>49.7</v>
-      </c>
-      <c r="F10" s="3">
-        <v>100</v>
-      </c>
-      <c r="G10" s="3">
-        <f t="shared" si="0"/>
-        <v>0.49700000000000005</v>
-      </c>
       <c r="H10">
         <v>0</v>
       </c>
@@ -4108,32 +4487,31 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" s="3">
-        <v>0.50700000000000001</v>
-      </c>
-      <c r="D11" t="s">
+        <v>874</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E11" s="5">
+        <v>220.005</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="E11" s="5">
-        <v>49.7</v>
-      </c>
-      <c r="F11" s="3">
-        <v>100</v>
-      </c>
-      <c r="G11" s="3">
-        <f t="shared" si="0"/>
-        <v>0.49700000000000005</v>
+      <c r="G11" s="3" t="s">
+        <v>156</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
-      <c r="I11">
-        <v>0.2</v>
+      <c r="I11" s="3">
+        <v>0.9</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -4149,20 +4527,20 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A12" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="B12" s="10">
+      <c r="A12" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" s="3">
         <v>1</v>
       </c>
       <c r="C12" s="3">
-        <v>874</v>
+        <v>213.91</v>
       </c>
       <c r="D12" s="3">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="E12" s="5">
-        <v>220.005</v>
+        <v>209.87799999999999</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>156</v>
@@ -4174,7 +4552,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="3">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -4190,20 +4568,20 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A13" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="B13" s="10">
+      <c r="A13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" s="3">
         <v>1</v>
       </c>
       <c r="C13" s="3">
-        <v>213.91</v>
+        <v>160.928</v>
       </c>
       <c r="D13" s="3">
         <v>0.8</v>
       </c>
       <c r="E13" s="5">
-        <v>209.87799999999999</v>
+        <v>133.22499999999999</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>156</v>
@@ -4232,19 +4610,19 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B14" s="3">
         <v>1</v>
       </c>
       <c r="C14" s="3">
-        <v>160.928</v>
+        <v>16000</v>
       </c>
       <c r="D14" s="3">
-        <v>0.8</v>
+        <v>0.05</v>
       </c>
       <c r="E14" s="5">
-        <v>133.22499999999999</v>
+        <v>2</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>156</v>
@@ -4256,7 +4634,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="3">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -4272,20 +4650,20 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A15" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="B15" s="11">
+      <c r="A15" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" s="3">
         <v>1</v>
       </c>
       <c r="C15" s="3">
-        <v>16000</v>
+        <v>200</v>
       </c>
       <c r="D15" s="3">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="E15" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>156</v>
@@ -4313,20 +4691,20 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A16" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="B16" s="11">
-        <v>1</v>
-      </c>
-      <c r="C16" s="3">
-        <v>200</v>
-      </c>
-      <c r="D16" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="E16" s="5">
-        <v>6</v>
+      <c r="A16" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" s="3">
+        <v>2</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>156</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>156</v>
@@ -4335,7 +4713,7 @@
         <v>156</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I16" s="3">
         <v>0.9</v>
@@ -4355,10 +4733,10 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>87</v>
+        <v>163</v>
       </c>
       <c r="B17" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>156</v>
@@ -4375,11 +4753,11 @@
       <c r="G17" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="H17">
-        <v>1000</v>
-      </c>
-      <c r="I17" s="3">
-        <v>0.9</v>
+      <c r="H17" t="s">
+        <v>156</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>156</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -4392,59 +4770,6 @@
       </c>
       <c r="M17" s="3">
         <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A18" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="B18" s="3">
-        <v>3</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="H18" t="s">
-        <v>156</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <v>1</v>
-      </c>
-      <c r="L18" s="3">
-        <v>0</v>
-      </c>
-      <c r="M18" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B27">
-        <f>(6.85*365)/39.1</f>
-        <v>63.945012787723783</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B28">
-        <f>0.28*365</f>
-        <v>102.2</v>
       </c>
     </row>
   </sheetData>
@@ -4452,7 +4777,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8507B781-AD72-4DC8-A4BE-7CF19625E49F}">
   <dimension ref="A1:P18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4714,7 +5039,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7418386-27DC-4709-93B5-642FE7B9EAEE}">
   <dimension ref="A1:Z42"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -6983,7 +7308,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{885072BE-048E-4823-9B10-4C85A9AD3529}">
   <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -7542,7 +7867,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{570365D2-CF0E-4D4C-9C66-9B0194DA64C1}">
   <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
